--- a/code/data/combined/cmb+dmul-w0wacdm-free.xlsx
+++ b/code/data/combined/cmb+dmul-w0wacdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39213913.99731913</v>
+        <v>44425444.09161822</v>
       </c>
       <c r="C2" t="n">
-        <v>-134286934.5265953</v>
+        <v>-148685611.4063865</v>
       </c>
       <c r="D2" t="n">
-        <v>40645477.10038732</v>
+        <v>46689835.98481975</v>
       </c>
       <c r="E2" t="n">
-        <v>-410392.9036168669</v>
+        <v>-468237.0929251655</v>
       </c>
       <c r="F2" t="n">
-        <v>-1418702.450820673</v>
+        <v>-1421460.027978511</v>
       </c>
       <c r="G2" t="n">
-        <v>882064.6768770375</v>
+        <v>1050448.297635525</v>
       </c>
       <c r="H2" t="n">
-        <v>-2580705.562161939</v>
+        <v>-2936361.213577654</v>
       </c>
       <c r="I2" t="n">
-        <v>6341212.527979546</v>
+        <v>7261795.86510236</v>
       </c>
       <c r="J2" t="n">
-        <v>1714925.701573917</v>
+        <v>1964134.815222068</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134286934.5343772</v>
+        <v>-148685611.4140785</v>
       </c>
       <c r="C3" t="n">
-        <v>887991069.0889354</v>
+        <v>895782919.2181739</v>
       </c>
       <c r="D3" t="n">
-        <v>-89476835.98196873</v>
+        <v>-111911248.9914472</v>
       </c>
       <c r="E3" t="n">
-        <v>15741702.57380962</v>
+        <v>16344774.50336654</v>
       </c>
       <c r="F3" t="n">
-        <v>6695175.623711858</v>
+        <v>6648185.514143971</v>
       </c>
       <c r="G3" t="n">
-        <v>-3840600.547837915</v>
+        <v>-4444658.216271537</v>
       </c>
       <c r="H3" t="n">
-        <v>7957657.046347632</v>
+        <v>8986371.166113341</v>
       </c>
       <c r="I3" t="n">
-        <v>-24772829.79962163</v>
+        <v>-27644008.25787808</v>
       </c>
       <c r="J3" t="n">
-        <v>-6679845.541142254</v>
+        <v>-7459016.137597967</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40645477.09939209</v>
+        <v>46689835.98404989</v>
       </c>
       <c r="C4" t="n">
-        <v>-89476835.9700062</v>
+        <v>-111911248.9805245</v>
       </c>
       <c r="D4" t="n">
-        <v>49444924.02612878</v>
+        <v>55547151.1077417</v>
       </c>
       <c r="E4" t="n">
-        <v>942916.4145253235</v>
+        <v>855710.4823788292</v>
       </c>
       <c r="F4" t="n">
-        <v>-1134934.082239027</v>
+        <v>-1159056.221435535</v>
       </c>
       <c r="G4" t="n">
-        <v>966618.6947894894</v>
+        <v>1147987.178450534</v>
       </c>
       <c r="H4" t="n">
-        <v>-2838565.593181915</v>
+        <v>-3240542.095590248</v>
       </c>
       <c r="I4" t="n">
-        <v>6579923.331829162</v>
+        <v>7621302.07475848</v>
       </c>
       <c r="J4" t="n">
-        <v>1782597.820424848</v>
+        <v>2064243.87282116</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-410392.9038400484</v>
+        <v>-468237.0932615901</v>
       </c>
       <c r="C5" t="n">
-        <v>15741702.57432984</v>
+        <v>16344774.50434161</v>
       </c>
       <c r="D5" t="n">
-        <v>942916.4142455689</v>
+        <v>855710.4819927253</v>
       </c>
       <c r="E5" t="n">
-        <v>982978.4599441644</v>
+        <v>1070203.214649057</v>
       </c>
       <c r="F5" t="n">
-        <v>24342.18684216631</v>
+        <v>43220.6730655439</v>
       </c>
       <c r="G5" t="n">
-        <v>-74077.02687820178</v>
+        <v>-81632.91826405819</v>
       </c>
       <c r="H5" t="n">
-        <v>-5276.187884396399</v>
+        <v>-4509.436011792288</v>
       </c>
       <c r="I5" t="n">
-        <v>-264044.0861786138</v>
+        <v>-294441.0110794668</v>
       </c>
       <c r="J5" t="n">
-        <v>-70664.21383152853</v>
+        <v>-78921.85737508669</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1418702.450887197</v>
+        <v>-1421460.028007777</v>
       </c>
       <c r="C6" t="n">
-        <v>6695175.624030709</v>
+        <v>6648185.51432426</v>
       </c>
       <c r="D6" t="n">
-        <v>-1134934.082301263</v>
+        <v>-1159056.221459675</v>
       </c>
       <c r="E6" t="n">
-        <v>24342.18684731469</v>
+        <v>43220.67306971976</v>
       </c>
       <c r="F6" t="n">
-        <v>747842.7102511218</v>
+        <v>748820.2786743471</v>
       </c>
       <c r="G6" t="n">
-        <v>107300.5174989925</v>
+        <v>106083.3443272555</v>
       </c>
       <c r="H6" t="n">
-        <v>41833.25559420413</v>
+        <v>40933.88476482166</v>
       </c>
       <c r="I6" t="n">
-        <v>-32207.17347625972</v>
+        <v>-36088.89669822926</v>
       </c>
       <c r="J6" t="n">
-        <v>-11083.48393571121</v>
+        <v>-12122.33602325436</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>882064.6768765828</v>
+        <v>1050448.297667751</v>
       </c>
       <c r="C7" t="n">
-        <v>-3840600.54752751</v>
+        <v>-4444658.216092148</v>
       </c>
       <c r="D7" t="n">
-        <v>966618.6948283484</v>
+        <v>1147987.178514698</v>
       </c>
       <c r="E7" t="n">
-        <v>-74077.02686912009</v>
+        <v>-81632.91825226454</v>
       </c>
       <c r="F7" t="n">
-        <v>107300.517501726</v>
+        <v>106083.3443286595</v>
       </c>
       <c r="G7" t="n">
-        <v>66677.42738641069</v>
+        <v>72577.55396690567</v>
       </c>
       <c r="H7" t="n">
-        <v>-71267.17444922663</v>
+        <v>-82481.03829771519</v>
       </c>
       <c r="I7" t="n">
-        <v>227892.1413572851</v>
+        <v>259238.0130066696</v>
       </c>
       <c r="J7" t="n">
-        <v>62139.7915736772</v>
+        <v>70629.44695235479</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2580705.562140899</v>
+        <v>-2936361.213564264</v>
       </c>
       <c r="C8" t="n">
-        <v>7957657.045720022</v>
+        <v>8986371.165524568</v>
       </c>
       <c r="D8" t="n">
-        <v>-2838565.59322973</v>
+        <v>-3240542.095629996</v>
       </c>
       <c r="E8" t="n">
-        <v>-5276.187901087917</v>
+        <v>-4509.436035875839</v>
       </c>
       <c r="F8" t="n">
-        <v>41833.25558969543</v>
+        <v>40933.88476287829</v>
       </c>
       <c r="G8" t="n">
-        <v>-71267.17444842035</v>
+        <v>-82481.03829493461</v>
       </c>
       <c r="H8" t="n">
-        <v>178548.4155608011</v>
+        <v>202883.0481117919</v>
       </c>
       <c r="I8" t="n">
-        <v>-437588.3424956283</v>
+        <v>-499559.9482145067</v>
       </c>
       <c r="J8" t="n">
-        <v>-118281.8521489658</v>
+        <v>-135053.4876085483</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6341212.528003023</v>
+        <v>7261795.865199298</v>
       </c>
       <c r="C9" t="n">
-        <v>-24772829.79819682</v>
+        <v>-27644008.25675835</v>
       </c>
       <c r="D9" t="n">
-        <v>6579923.332047432</v>
+        <v>7621302.075009696</v>
       </c>
       <c r="E9" t="n">
-        <v>-264044.0861357242</v>
+        <v>-294441.0110186048</v>
       </c>
       <c r="F9" t="n">
-        <v>-32207.17346289614</v>
+        <v>-36088.89669174528</v>
       </c>
       <c r="G9" t="n">
-        <v>227892.1413583281</v>
+        <v>259238.0130042383</v>
       </c>
       <c r="H9" t="n">
-        <v>-437588.3425013856</v>
+        <v>-499559.9482238864</v>
       </c>
       <c r="I9" t="n">
-        <v>1200137.243677179</v>
+        <v>1368239.033282841</v>
       </c>
       <c r="J9" t="n">
-        <v>325354.973017031</v>
+        <v>370869.5218364741</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1714925.701579961</v>
+        <v>1964134.815248647</v>
       </c>
       <c r="C10" t="n">
-        <v>-6679845.540753992</v>
+        <v>-7459016.137297169</v>
       </c>
       <c r="D10" t="n">
-        <v>1782597.82048374</v>
+        <v>2064243.872889325</v>
       </c>
       <c r="E10" t="n">
-        <v>-70664.21381987297</v>
+        <v>-78921.85735852469</v>
       </c>
       <c r="F10" t="n">
-        <v>-11083.48393207158</v>
+        <v>-12122.33602150157</v>
       </c>
       <c r="G10" t="n">
-        <v>62139.79157394613</v>
+        <v>70629.44695170497</v>
       </c>
       <c r="H10" t="n">
-        <v>-118281.852150505</v>
+        <v>-135053.4876111113</v>
       </c>
       <c r="I10" t="n">
-        <v>325354.9730169597</v>
+        <v>370869.521836526</v>
       </c>
       <c r="J10" t="n">
-        <v>88478.61545406954</v>
+        <v>100802.0124069634</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+dmul-w0wacdm-free.xlsx
+++ b/code/data/combined/cmb+dmul-w0wacdm-free.xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44425444.09161822</v>
+        <v>43575294.85333394</v>
       </c>
       <c r="C2" t="n">
-        <v>-148685611.4063865</v>
+        <v>-145846347.9043355</v>
       </c>
       <c r="D2" t="n">
-        <v>46689835.98481975</v>
+        <v>45770888.47204529</v>
       </c>
       <c r="E2" t="n">
-        <v>-468237.0929251655</v>
+        <v>-460982.2861277387</v>
       </c>
       <c r="F2" t="n">
-        <v>-1421460.027978511</v>
+        <v>-1413843.634451086</v>
       </c>
       <c r="G2" t="n">
-        <v>1050448.297635525</v>
+        <v>1023557.718635508</v>
       </c>
       <c r="H2" t="n">
-        <v>-2936361.213577654</v>
+        <v>-2876521.124143769</v>
       </c>
       <c r="I2" t="n">
-        <v>7261795.86510236</v>
+        <v>7110737.35681438</v>
       </c>
       <c r="J2" t="n">
-        <v>1964134.815222068</v>
+        <v>1923225.024206066</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-148685611.4140785</v>
+        <v>-145846347.8921299</v>
       </c>
       <c r="C3" t="n">
-        <v>895782919.2181739</v>
+        <v>876933849.0457015</v>
       </c>
       <c r="D3" t="n">
-        <v>-111911248.9914472</v>
+        <v>-110082289.0299681</v>
       </c>
       <c r="E3" t="n">
-        <v>16344774.50336654</v>
+        <v>16113321.63754462</v>
       </c>
       <c r="F3" t="n">
-        <v>6648185.514143971</v>
+        <v>6575874.492913395</v>
       </c>
       <c r="G3" t="n">
-        <v>-4444658.216271537</v>
+        <v>-4351201.15487885</v>
       </c>
       <c r="H3" t="n">
-        <v>8986371.166113341</v>
+        <v>8808024.177754324</v>
       </c>
       <c r="I3" t="n">
-        <v>-27644008.25787808</v>
+        <v>-27114073.02801316</v>
       </c>
       <c r="J3" t="n">
-        <v>-7459016.137597967</v>
+        <v>-7315638.473765252</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46689835.98404989</v>
+        <v>45770888.47338015</v>
       </c>
       <c r="C4" t="n">
-        <v>-111911248.9805245</v>
+        <v>-110082289.0476781</v>
       </c>
       <c r="D4" t="n">
-        <v>55547151.1077417</v>
+        <v>54387206.99925124</v>
       </c>
       <c r="E4" t="n">
-        <v>855710.4823788292</v>
+        <v>837194.9054130138</v>
       </c>
       <c r="F4" t="n">
-        <v>-1159056.221435535</v>
+        <v>-1155120.54074441</v>
       </c>
       <c r="G4" t="n">
-        <v>1147987.178450534</v>
+        <v>1119448.476593135</v>
       </c>
       <c r="H4" t="n">
-        <v>-3240542.095590248</v>
+        <v>-3173093.46352515</v>
       </c>
       <c r="I4" t="n">
-        <v>7621302.07475848</v>
+        <v>7461160.876074535</v>
       </c>
       <c r="J4" t="n">
-        <v>2064243.87282116</v>
+        <v>2020852.794805089</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-468237.0932615901</v>
+        <v>-460982.2856275192</v>
       </c>
       <c r="C5" t="n">
-        <v>16344774.50434161</v>
+        <v>16113321.63612245</v>
       </c>
       <c r="D5" t="n">
-        <v>855710.4819927253</v>
+        <v>837194.9059776743</v>
       </c>
       <c r="E5" t="n">
-        <v>1070203.214649057</v>
+        <v>1062321.036090149</v>
       </c>
       <c r="F5" t="n">
-        <v>43220.6730655439</v>
+        <v>43141.09558549104</v>
       </c>
       <c r="G5" t="n">
-        <v>-81632.91826405819</v>
+        <v>-81084.23472349952</v>
       </c>
       <c r="H5" t="n">
-        <v>-4509.436011792288</v>
+        <v>-4385.553138155771</v>
       </c>
       <c r="I5" t="n">
-        <v>-294441.0110794668</v>
+        <v>-292019.9767182142</v>
       </c>
       <c r="J5" t="n">
-        <v>-78921.85737508669</v>
+        <v>-78273.66676132291</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1421460.028007777</v>
+        <v>-1413843.634307361</v>
       </c>
       <c r="C6" t="n">
-        <v>6648185.51432426</v>
+        <v>6575874.492638189</v>
       </c>
       <c r="D6" t="n">
-        <v>-1159056.221459675</v>
+        <v>-1155120.540567585</v>
       </c>
       <c r="E6" t="n">
-        <v>43220.67306971976</v>
+        <v>43141.09559106994</v>
       </c>
       <c r="F6" t="n">
-        <v>748820.2786743471</v>
+        <v>744664.3838412075</v>
       </c>
       <c r="G6" t="n">
-        <v>106083.3443272555</v>
+        <v>105952.2139535038</v>
       </c>
       <c r="H6" t="n">
-        <v>40933.88476482166</v>
+        <v>40551.41764118084</v>
       </c>
       <c r="I6" t="n">
-        <v>-36088.89669822926</v>
+        <v>-35039.1917764899</v>
       </c>
       <c r="J6" t="n">
-        <v>-12122.33602325436</v>
+        <v>-11831.17047170399</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1050448.297667751</v>
+        <v>1023557.718617914</v>
       </c>
       <c r="C7" t="n">
-        <v>-4444658.216092148</v>
+        <v>-4351201.155177975</v>
       </c>
       <c r="D7" t="n">
-        <v>1147987.178514698</v>
+        <v>1119448.476534951</v>
       </c>
       <c r="E7" t="n">
-        <v>-81632.91825226454</v>
+        <v>-81084.23473786868</v>
       </c>
       <c r="F7" t="n">
-        <v>106083.3443286595</v>
+        <v>105952.213949642</v>
       </c>
       <c r="G7" t="n">
-        <v>72577.55396690567</v>
+        <v>71670.12458642402</v>
       </c>
       <c r="H7" t="n">
-        <v>-82481.03829771519</v>
+        <v>-80596.34559541891</v>
       </c>
       <c r="I7" t="n">
-        <v>259238.0130066696</v>
+        <v>254362.8094482867</v>
       </c>
       <c r="J7" t="n">
-        <v>70629.44695235479</v>
+        <v>69310.00985406384</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2936361.213564264</v>
+        <v>-2876521.124175293</v>
       </c>
       <c r="C8" t="n">
-        <v>8986371.165524568</v>
+        <v>8808024.178686062</v>
       </c>
       <c r="D8" t="n">
-        <v>-3240542.095629996</v>
+        <v>-3173093.463468927</v>
       </c>
       <c r="E8" t="n">
-        <v>-4509.436035875839</v>
+        <v>-4385.553103268733</v>
       </c>
       <c r="F8" t="n">
-        <v>40933.88476287829</v>
+        <v>40551.41765146422</v>
       </c>
       <c r="G8" t="n">
-        <v>-82481.03829493461</v>
+        <v>-80596.34559754368</v>
       </c>
       <c r="H8" t="n">
-        <v>202883.0481117919</v>
+        <v>198605.9734341088</v>
       </c>
       <c r="I8" t="n">
-        <v>-499559.9482145067</v>
+        <v>-488996.6760100981</v>
       </c>
       <c r="J8" t="n">
-        <v>-135053.4876085483</v>
+        <v>-132192.3544289305</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7261795.865199298</v>
+        <v>7110737.356720526</v>
       </c>
       <c r="C9" t="n">
-        <v>-27644008.25675835</v>
+        <v>-27114073.02983125</v>
       </c>
       <c r="D9" t="n">
-        <v>7621302.075009696</v>
+        <v>7461160.875740049</v>
       </c>
       <c r="E9" t="n">
-        <v>-294441.0110186048</v>
+        <v>-292019.9768035268</v>
       </c>
       <c r="F9" t="n">
-        <v>-36088.89669174528</v>
+        <v>-35039.19179982935</v>
       </c>
       <c r="G9" t="n">
-        <v>259238.0130042383</v>
+        <v>254362.8094486108</v>
       </c>
       <c r="H9" t="n">
-        <v>-499559.9482238864</v>
+        <v>-488996.6759982133</v>
       </c>
       <c r="I9" t="n">
-        <v>1368239.033282841</v>
+        <v>1341152.501283286</v>
       </c>
       <c r="J9" t="n">
-        <v>370869.5218364741</v>
+        <v>363535.3611557242</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1964134.815248647</v>
+        <v>1923225.024180804</v>
       </c>
       <c r="C10" t="n">
-        <v>-7459016.137297169</v>
+        <v>-7315638.474254205</v>
       </c>
       <c r="D10" t="n">
-        <v>2064243.872889325</v>
+        <v>2020852.794715235</v>
       </c>
       <c r="E10" t="n">
-        <v>-78921.85735852469</v>
+        <v>-78273.6667844889</v>
       </c>
       <c r="F10" t="n">
-        <v>-12122.33602150157</v>
+        <v>-11831.17047802137</v>
       </c>
       <c r="G10" t="n">
-        <v>70629.44695170497</v>
+        <v>69310.00985415606</v>
       </c>
       <c r="H10" t="n">
-        <v>-135053.4876111113</v>
+        <v>-132192.3544257263</v>
       </c>
       <c r="I10" t="n">
-        <v>370869.521836526</v>
+        <v>363535.3611557505</v>
       </c>
       <c r="J10" t="n">
-        <v>100802.0124069634</v>
+        <v>98816.13669208415</v>
       </c>
     </row>
   </sheetData>
